--- a/artfynd/A 14562-2025 artfynd.xlsx
+++ b/artfynd/A 14562-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89511944</v>
+        <v>89511959</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617952.1265491744</v>
+        <v>618284</v>
       </c>
       <c r="R2" t="n">
-        <v>6744496.932322461</v>
+        <v>6744488</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89511957</v>
+        <v>89511916</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618268.8108463916</v>
+        <v>618272</v>
       </c>
       <c r="R3" t="n">
-        <v>6744531.827081406</v>
+        <v>6744436</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89511919</v>
+        <v>97604780</v>
       </c>
       <c r="B4" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618099.8724974967</v>
+        <v>618241</v>
       </c>
       <c r="R4" t="n">
-        <v>6744465.204878656</v>
+        <v>6744489</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,22 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89511918</v>
+        <v>89511917</v>
       </c>
       <c r="B5" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618177.1130327967</v>
+        <v>618189</v>
       </c>
       <c r="R5" t="n">
-        <v>6744465.809856463</v>
+        <v>6744449</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89511954</v>
+        <v>89511956</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618223.9528552326</v>
+        <v>618238</v>
       </c>
       <c r="R6" t="n">
-        <v>6744586.971065576</v>
+        <v>6744562</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89511950</v>
+        <v>89511961</v>
       </c>
       <c r="B7" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618144.8497552576</v>
+        <v>618388</v>
       </c>
       <c r="R7" t="n">
-        <v>6744613.153689215</v>
+        <v>6744496</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,19 +1248,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89511956</v>
+        <v>89511918</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618237.9811767292</v>
+        <v>618177</v>
       </c>
       <c r="R8" t="n">
-        <v>6744562.049862053</v>
+        <v>6744466</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,19 +1349,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89511955</v>
+        <v>89511952</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618220.1548466542</v>
+        <v>618174</v>
       </c>
       <c r="R9" t="n">
-        <v>6744568.782011713</v>
+        <v>6744603</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1560,19 +1450,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89511953</v>
+        <v>89511950</v>
       </c>
       <c r="B10" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618189.891387632</v>
+        <v>618145</v>
       </c>
       <c r="R10" t="n">
-        <v>6744581.936874933</v>
+        <v>6744613</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,19 +1551,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89511951</v>
+        <v>89511958</v>
       </c>
       <c r="B11" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,39 +1595,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hittsjömyran, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618154.0130729293</v>
+        <v>618282</v>
       </c>
       <c r="R11" t="n">
-        <v>6744602.228817413</v>
+        <v>6744500</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1797,19 +1652,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,37 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89511952</v>
+        <v>89511954</v>
       </c>
       <c r="B12" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618174.0389724651</v>
+        <v>618224</v>
       </c>
       <c r="R12" t="n">
-        <v>6744602.892149815</v>
+        <v>6744587</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1913,19 +1753,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,37 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89511958</v>
+        <v>89511962</v>
       </c>
       <c r="B13" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1996,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618282.0891538205</v>
+        <v>618396</v>
       </c>
       <c r="R13" t="n">
-        <v>6744500.045892362</v>
+        <v>6744504</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2029,19 +1854,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,37 +1887,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89511962</v>
+        <v>89511953</v>
       </c>
       <c r="B14" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2112,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618395.8981438614</v>
+        <v>618190</v>
       </c>
       <c r="R14" t="n">
-        <v>6744503.821111117</v>
+        <v>6744582</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2145,19 +1955,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,50 +1988,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89511961</v>
+        <v>89511951</v>
       </c>
       <c r="B15" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hittsjömyran, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618387.837237371</v>
+        <v>618154</v>
       </c>
       <c r="R15" t="n">
-        <v>6744496.230499243</v>
+        <v>6744602</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2261,19 +2061,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2304,37 +2094,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89511916</v>
+        <v>89511920</v>
       </c>
       <c r="B16" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>220785</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2344,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618271.9796436517</v>
+        <v>618026</v>
       </c>
       <c r="R16" t="n">
-        <v>6744436.243450016</v>
+        <v>6744433</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2377,19 +2162,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,37 +2195,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89511917</v>
+        <v>89511944</v>
       </c>
       <c r="B17" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220785</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2460,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618188.9129688067</v>
+        <v>617952</v>
       </c>
       <c r="R17" t="n">
-        <v>6744449.113396763</v>
+        <v>6744497</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2493,19 +2263,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2536,37 +2296,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89511959</v>
+        <v>89511955</v>
       </c>
       <c r="B18" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2576,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>618283.9587354973</v>
+        <v>618220</v>
       </c>
       <c r="R18" t="n">
-        <v>6744487.902721005</v>
+        <v>6744569</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2609,19 +2364,9 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-05-29</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2652,37 +2397,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97604780</v>
+        <v>89511957</v>
       </c>
       <c r="B19" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2692,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>618240.8940979389</v>
+        <v>618269</v>
       </c>
       <c r="R19" t="n">
-        <v>6744488.916166548</v>
+        <v>6744532</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2722,22 +2462,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,6 +2491,309 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>89511919</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hittsjömyran, Gstr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>618100</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6744465</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-05-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-05-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>89511945</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hittsjömyran, Gstr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>617941</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6744532</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-05-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-05-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>89511921</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hittsjömyran, Gstr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>618026</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6744433</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-05-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-05-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
         <is>
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>

--- a/artfynd/A 14562-2025 artfynd.xlsx
+++ b/artfynd/A 14562-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511959</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511916</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97604780</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511917</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511956</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511961</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511918</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511952</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511950</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511958</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511954</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511962</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511953</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511951</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511920</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2293,6 +2373,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511944</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2394,6 +2479,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511955</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2495,6 +2585,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511957</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2596,6 +2691,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511919</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2697,6 +2797,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511945</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2798,8 +2903,36 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89511921</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>